--- a/03-P2-ux-design/02-persona-mapping.xlsx
+++ b/03-P2-ux-design/02-persona-mapping.xlsx
@@ -157,10 +157,10 @@
     <t>Primary</t>
   </si>
   <si>
-    <t>Người chạy giữa hai slot</t>
-  </si>
-  <si>
-    <t>20 tuổi, SV năm 2 KTPM, ở KTX</t>
+    <t>Người chạy giữa hai tiết</t>
+  </si>
+  <si>
+    <t>20 tuổi, SV năm 2 KTPM, học cả ngày trên campus</t>
   </si>
   <si>
     <t>Hành lang / đi bộ giữa hai tòa, một tay, mạng chập chờn, ngoài nắng</t>
@@ -169,7 +169,7 @@
     <t>Có đồ ăn trong giờ nghỉ không trễ lớp; biết món đã xong; biết đúng số tiền</t>
   </si>
   <si>
-    <t>Khi chỉ có 15 phút giữa hai slot, tôi muốn đặt trước và ghé quầy lấy ngay, để ăn kịp mà không xếp hàng</t>
+    <t>Khi chỉ có 15 phút giữa hai tiết, tôi muốn đặt trước và ghé quầy lấy ngay, để ăn kịp mà không xếp hàng</t>
   </si>
   <si>
     <t>Bỏ bữa sáng, mua bù lúc nghỉ; thấy hàng dài thì bỏ; từng đặt Grab phải ra cổng; trả QR</t>
@@ -184,7 +184,7 @@
     <t>15 phút nghỉ (~5 phút đi bộ); một tay; mạng yếu; không muốn đăng ký</t>
   </si>
   <si>
-    <t>S1 đặt cuối slot, hẹn giờ, lấy theo mã; S2 thanh toán timeout → tiền mặt, giữ giỏ</t>
+    <t>S1 đặt cuối tiết, hẹn giờ, lấy theo mã; S2 thanh toán timeout → tiền mặt, giữ giỏ</t>
   </si>
   <si>
     <t>Đặt xong đơn &lt; 35 giây, ≤ 8 chạm (Flow 1)</t>
@@ -214,7 +214,7 @@
     <t>19 tuổi, SV năm 1 Thiết kế, ở trọ</t>
   </si>
   <si>
-    <t>Ngồi hành lang giữa hai slot sáng, hai tay, ví MoMo</t>
+    <t>Ngồi hành lang giữa hai tiết sáng, hai tay, ví MoMo</t>
   </si>
   <si>
     <t>Ăn trong ngân sách ~40.000đ/ngày; thấy tổng tiền thật trước khi đặt</t>

--- a/03-P2-ux-design/02-persona-mapping.xlsx
+++ b/03-P2-ux-design/02-persona-mapping.xlsx
@@ -157,7 +157,7 @@
     <t>Primary</t>
   </si>
   <si>
-    <t>Người chạy giữa hai tiết</t>
+    <t>Người chạy giữa hai slot</t>
   </si>
   <si>
     <t>20 tuổi, SV năm 2 KTPM, học cả ngày trên campus</t>
@@ -169,7 +169,7 @@
     <t>Có đồ ăn trong giờ nghỉ không trễ lớp; biết món đã xong; biết đúng số tiền</t>
   </si>
   <si>
-    <t>Khi chỉ có 15 phút giữa hai tiết, tôi muốn đặt trước và ghé quầy lấy ngay, để ăn kịp mà không xếp hàng</t>
+    <t>Khi chỉ có 15 phút giữa hai slot, tôi muốn đặt trước và ghé quầy lấy ngay, để ăn kịp mà không xếp hàng</t>
   </si>
   <si>
     <t>Bỏ bữa sáng, mua bù lúc nghỉ; thấy hàng dài thì bỏ; từng đặt Grab phải ra cổng; trả QR</t>
@@ -184,7 +184,7 @@
     <t>15 phút nghỉ (~5 phút đi bộ); một tay; mạng yếu; không muốn đăng ký</t>
   </si>
   <si>
-    <t>S1 đặt cuối tiết, hẹn giờ, lấy theo mã; S2 thanh toán timeout → tiền mặt, giữ giỏ</t>
+    <t>S1 đặt cuối slot, hẹn giờ, lấy theo mã; S2 thanh toán timeout → tiền mặt, giữ giỏ</t>
   </si>
   <si>
     <t>Đặt xong đơn &lt; 35 giây, ≤ 8 chạm (Flow 1)</t>
@@ -214,7 +214,7 @@
     <t>19 tuổi, SV năm 1 Thiết kế, ở trọ</t>
   </si>
   <si>
-    <t>Ngồi hành lang giữa hai tiết sáng, hai tay, ví MoMo</t>
+    <t>Ngồi hành lang giữa hai slot sáng, hai tay, ví MoMo</t>
   </si>
   <si>
     <t>Ăn trong ngân sách ~40.000đ/ngày; thấy tổng tiền thật trước khi đặt</t>
